--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755523330_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008438734620987253</v>
       </c>
       <c r="C2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>40115327</v>
+        <v>4050116</v>
       </c>
       <c r="L2" t="n">
-        <v>21840007</v>
+        <v>1835381</v>
       </c>
       <c r="M2" t="n">
-        <v>5268952</v>
+        <v>368060</v>
       </c>
       <c r="N2" t="n">
-        <v>260982</v>
+        <v>8010</v>
       </c>
       <c r="O2" t="n">
-        <v>3135031</v>
+        <v>207830</v>
       </c>
       <c r="P2" t="n">
-        <v>1191786</v>
+        <v>67612</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999805092811584</v>
+        <v>0.999925971031189</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8588496446609497</v>
+        <v>0.7551133036613464</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7395569086074829</v>
+        <v>0.5672262907028198</v>
       </c>
       <c r="T2" t="n">
-        <v>0.675711989402771</v>
+        <v>0.4452110826969147</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3327672183513641</v>
+        <v>0.06688600033521652</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7188786268234253</v>
+        <v>0.4938491582870483</v>
       </c>
       <c r="W2" t="n">
-        <v>0.825826108455658</v>
+        <v>0.6593140959739685</v>
       </c>
       <c r="X2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>57117420</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>43513679</v>
+        <v>4801660</v>
       </c>
       <c r="AG2" t="n">
-        <v>26954665</v>
+        <v>3018155</v>
       </c>
       <c r="AH2" t="n">
-        <v>7220207</v>
+        <v>805700</v>
       </c>
       <c r="AI2" t="n">
-        <v>532493</v>
+        <v>59334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4137274</v>
+        <v>460847</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9561951160430908</v>
+        <v>0.9551666378974915</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114695191383362</v>
+        <v>0.9119651317596436</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580380082130432</v>
+        <v>0.8582442998886108</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618042588233948</v>
+        <v>0.660926342010498</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019699692726135</v>
+        <v>0.9019715189933777</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002022102987121896</v>
       </c>
       <c r="C3" t="n">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="D3" t="n">
-        <v>40115327</v>
+        <v>4050116</v>
       </c>
       <c r="E3" t="n">
-        <v>5173482</v>
+        <v>923664</v>
       </c>
       <c r="F3" t="n">
-        <v>132683</v>
+        <v>36176</v>
       </c>
       <c r="G3" t="n">
-        <v>12088</v>
+        <v>2635</v>
       </c>
       <c r="H3" t="n">
-        <v>8653</v>
+        <v>2415</v>
       </c>
       <c r="I3" t="n">
-        <v>513</v>
+        <v>165</v>
       </c>
       <c r="J3" t="n">
-        <v>90625467</v>
+        <v>10069150</v>
       </c>
       <c r="K3" t="n">
-        <v>95708247</v>
+        <v>10087303</v>
       </c>
       <c r="L3" t="n">
-        <v>110427866</v>
+        <v>11696875</v>
       </c>
       <c r="M3" t="n">
-        <v>136792371</v>
+        <v>15016715</v>
       </c>
       <c r="N3" t="n">
-        <v>146415334</v>
+        <v>16214377</v>
       </c>
       <c r="O3" t="n">
-        <v>141928386</v>
+        <v>15691592</v>
       </c>
       <c r="P3" t="n">
-        <v>145751834</v>
+        <v>16187377</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8827638626098633</v>
+        <v>0.8075640201568604</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7372170686721802</v>
+        <v>0.5530264973640442</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6255470514297485</v>
+        <v>0.3912884593009949</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3240523040294647</v>
+        <v>0.08912179619073868</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6830664277076721</v>
+        <v>0.4063934087753296</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6846165657043457</v>
+        <v>0.3490804731845856</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43513679</v>
+        <v>4801660</v>
       </c>
       <c r="Z3" t="n">
-        <v>1789967</v>
+        <v>198183</v>
       </c>
       <c r="AA3" t="n">
-        <v>77049</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>61571</v>
+        <v>6873</v>
       </c>
       <c r="AC3" t="n">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90626580</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>100307692</v>
+        <v>11175395</v>
       </c>
       <c r="AG3" t="n">
-        <v>115500975</v>
+        <v>12805854</v>
       </c>
       <c r="AH3" t="n">
-        <v>138126469</v>
+        <v>15342287</v>
       </c>
       <c r="AI3" t="n">
-        <v>146666515</v>
+        <v>16295683</v>
       </c>
       <c r="AJ3" t="n">
-        <v>142704700</v>
+        <v>15854513</v>
       </c>
       <c r="AK3" t="n">
-        <v>145883883</v>
+        <v>16209047</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575468301773071</v>
+        <v>0.9574164748191833</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098641276359558</v>
+        <v>0.9094131588935852</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572063446044922</v>
+        <v>0.8565481305122375</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611781120300293</v>
+        <v>0.6601688861846924</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.901436984539032</v>
+        <v>0.9011460542678833</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03192845045564235</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>6144525</v>
+        <v>1201302</v>
       </c>
       <c r="E4" t="n">
-        <v>21840007</v>
+        <v>1835381</v>
       </c>
       <c r="F4" t="n">
-        <v>1409227</v>
+        <v>231537</v>
       </c>
       <c r="G4" t="n">
-        <v>72411</v>
+        <v>16444</v>
       </c>
       <c r="H4" t="n">
-        <v>147068</v>
+        <v>31431</v>
       </c>
       <c r="I4" t="n">
-        <v>11661</v>
+        <v>2686</v>
       </c>
       <c r="J4" t="n">
-        <v>1113</v>
+        <v>470</v>
       </c>
       <c r="K4" t="n">
-        <v>6592880</v>
+        <v>1313471</v>
       </c>
       <c r="L4" t="n">
-        <v>7691199</v>
+        <v>1400331</v>
       </c>
       <c r="M4" t="n">
-        <v>2528678</v>
+        <v>458649</v>
       </c>
       <c r="N4" t="n">
-        <v>523296</v>
+        <v>111746</v>
       </c>
       <c r="O4" t="n">
-        <v>1225971</v>
+        <v>213007</v>
       </c>
       <c r="P4" t="n">
-        <v>251358</v>
+        <v>34937</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999902844429016</v>
+        <v>0.9999629855155945</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8706425428390503</v>
+        <v>0.7804583311080933</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7383851408958435</v>
+        <v>0.5600363612174988</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6496625542640686</v>
+        <v>0.4165117740631104</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3283519446849823</v>
+        <v>0.07641926407814026</v>
       </c>
       <c r="V4" t="n">
-        <v>0.70051509141922</v>
+        <v>0.4458732604980469</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7486205697059631</v>
+        <v>0.4564754366874695</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1861428</v>
+        <v>210622</v>
       </c>
       <c r="Z4" t="n">
-        <v>26954665</v>
+        <v>3018155</v>
       </c>
       <c r="AA4" t="n">
-        <v>748119</v>
+        <v>83217</v>
       </c>
       <c r="AB4" t="n">
-        <v>49825</v>
+        <v>5601</v>
       </c>
       <c r="AC4" t="n">
-        <v>10286</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1993435</v>
+        <v>225379</v>
       </c>
       <c r="AG4" t="n">
-        <v>2618090</v>
+        <v>291352</v>
       </c>
       <c r="AH4" t="n">
-        <v>1194580</v>
+        <v>133077</v>
       </c>
       <c r="AI4" t="n">
-        <v>272115</v>
+        <v>30440</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449657</v>
+        <v>50086</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568704962730408</v>
+        <v>0.9562901854515076</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106661081314087</v>
+        <v>0.9106873869895935</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576220273971558</v>
+        <v>0.857395350933075</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614910364151001</v>
+        <v>0.6605474352836609</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901703417301178</v>
+        <v>0.9015586376190186</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>313207</v>
+        <v>83120</v>
       </c>
       <c r="E5" t="n">
-        <v>2070708</v>
+        <v>369801</v>
       </c>
       <c r="F5" t="n">
-        <v>5268952</v>
+        <v>368060</v>
       </c>
       <c r="G5" t="n">
-        <v>170605</v>
+        <v>31074</v>
       </c>
       <c r="H5" t="n">
-        <v>549923</v>
+        <v>79323</v>
       </c>
       <c r="I5" t="n">
-        <v>49454</v>
+        <v>9214</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5327546</v>
+        <v>965110</v>
       </c>
       <c r="L5" t="n">
-        <v>7784928</v>
+        <v>1483413</v>
       </c>
       <c r="M5" t="n">
-        <v>3153999</v>
+        <v>572576</v>
       </c>
       <c r="N5" t="n">
-        <v>544388</v>
+        <v>81867</v>
       </c>
       <c r="O5" t="n">
-        <v>1454612</v>
+        <v>303571</v>
       </c>
       <c r="P5" t="n">
-        <v>549022</v>
+        <v>126074</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999924898147583</v>
+        <v>0.9999713897705078</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9193170070648193</v>
+        <v>0.8611975312232971</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8952503800392151</v>
+        <v>0.8243333101272583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9615370035171509</v>
+        <v>0.9371817111968994</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9927734136581421</v>
+        <v>0.9882058501243591</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9818565845489502</v>
+        <v>0.9685320258140564</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9945826530456543</v>
+        <v>0.9901918172836304</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72813</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>771695</v>
+        <v>86892</v>
       </c>
       <c r="AA5" t="n">
-        <v>7220207</v>
+        <v>805700</v>
       </c>
       <c r="AB5" t="n">
-        <v>89834</v>
+        <v>10028</v>
       </c>
       <c r="AC5" t="n">
-        <v>262705</v>
+        <v>29263</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1929194</v>
+        <v>213566</v>
       </c>
       <c r="AG5" t="n">
-        <v>2670270</v>
+        <v>300639</v>
       </c>
       <c r="AH5" t="n">
-        <v>1202744</v>
+        <v>134936</v>
       </c>
       <c r="AI5" t="n">
-        <v>272877</v>
+        <v>30543</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452369</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734498262405396</v>
+        <v>0.9732611179351807</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642059206962585</v>
+        <v>0.9639381766319275</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837738275527954</v>
+        <v>0.9836736917495728</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963112473487854</v>
+        <v>0.9962851405143738</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938946962356567</v>
+        <v>0.993869423866272</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382031917572</v>
+        <v>0.998377799987793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>208</v>
+        <v>53</v>
       </c>
       <c r="D6" t="n">
-        <v>114141</v>
+        <v>19782</v>
       </c>
       <c r="E6" t="n">
-        <v>164331</v>
+        <v>25154</v>
       </c>
       <c r="F6" t="n">
-        <v>180211</v>
+        <v>26855</v>
       </c>
       <c r="G6" t="n">
-        <v>260982</v>
+        <v>8010</v>
       </c>
       <c r="H6" t="n">
-        <v>77287</v>
+        <v>8924</v>
       </c>
       <c r="I6" t="n">
-        <v>8210</v>
+        <v>1099</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58711</v>
+        <v>6601</v>
       </c>
       <c r="Z6" t="n">
-        <v>48403</v>
+        <v>5386</v>
       </c>
       <c r="AA6" t="n">
-        <v>98482</v>
+        <v>11048</v>
       </c>
       <c r="AB6" t="n">
-        <v>532493</v>
+        <v>59334</v>
       </c>
       <c r="AC6" t="n">
-        <v>62952</v>
+        <v>7027</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="D7" t="n">
-        <v>20261</v>
+        <v>8915</v>
       </c>
       <c r="E7" t="n">
-        <v>260343</v>
+        <v>73808</v>
       </c>
       <c r="F7" t="n">
-        <v>751096</v>
+        <v>146605</v>
       </c>
       <c r="G7" t="n">
-        <v>241214</v>
+        <v>52351</v>
       </c>
       <c r="H7" t="n">
-        <v>3135031</v>
+        <v>207830</v>
       </c>
       <c r="I7" t="n">
-        <v>181520</v>
+        <v>21773</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7296</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267949</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68492</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4137274</v>
+        <v>460847</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>462</v>
+        <v>186</v>
       </c>
       <c r="D8" t="n">
-        <v>746</v>
+        <v>352</v>
       </c>
       <c r="E8" t="n">
-        <v>22335</v>
+        <v>7904</v>
       </c>
       <c r="F8" t="n">
-        <v>55461</v>
+        <v>17476</v>
       </c>
       <c r="G8" t="n">
-        <v>26978</v>
+        <v>9242</v>
       </c>
       <c r="H8" t="n">
-        <v>443040</v>
+        <v>90914</v>
       </c>
       <c r="I8" t="n">
-        <v>1191786</v>
+        <v>67612</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
